--- a/public/import_template/v0.2node/node_init_table.xlsx
+++ b/public/import_template/v0.2node/node_init_table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\ddit\code\umi_max.250519_master\public\import_template\v0.2node\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\ddit\code\umi_max.260226_github\public\import_template\v0.2node\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23EE7629-4235-4989-B5D9-BF3262751631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1E1E90-D928-45A1-A55D-61E6D14E2AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1402,7 +1402,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1436,12 +1436,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1540,7 +1534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1575,20 +1569,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1596,11 +1581,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2503,13 +2494,13 @@
       <c r="G36" s="3"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="21" t="s">
         <v>335</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="21" t="s">
         <v>333</v>
       </c>
       <c r="D37" s="3"/>
@@ -3524,183 +3515,183 @@
       <c r="G103" s="7"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" s="16" t="s">
+      <c r="A104" s="14" t="s">
         <v>371</v>
       </c>
-      <c r="B104" s="16" t="s">
+      <c r="B104" s="14" t="s">
         <v>379</v>
       </c>
-      <c r="C104" s="16" t="s">
+      <c r="C104" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="D104" s="16"/>
-      <c r="E104" s="17"/>
-      <c r="F104" s="17"/>
-      <c r="G104" s="17" t="s">
+      <c r="D104" s="14"/>
+      <c r="E104" s="15"/>
+      <c r="F104" s="15"/>
+      <c r="G104" s="15" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" s="20" t="s">
+      <c r="A105" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="B105" s="16" t="s">
+      <c r="B105" s="14" t="s">
         <v>382</v>
       </c>
       <c r="C105" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D105" s="20"/>
+      <c r="D105" s="17"/>
       <c r="E105" s="7"/>
       <c r="F105" s="7"/>
       <c r="G105" s="7"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A106" s="20" t="s">
+      <c r="A106" s="17" t="s">
         <v>372</v>
       </c>
-      <c r="B106" s="16" t="s">
+      <c r="B106" s="14" t="s">
         <v>383</v>
       </c>
       <c r="C106" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="D106" s="20"/>
+      <c r="D106" s="17"/>
       <c r="E106" s="7"/>
       <c r="F106" s="7"/>
       <c r="G106" s="7"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" s="20" t="s">
+      <c r="A107" s="18" t="s">
         <v>376</v>
       </c>
-      <c r="B107" s="20" t="s">
+      <c r="B107" s="18" t="s">
         <v>378</v>
       </c>
-      <c r="C107" s="12" t="s">
+      <c r="C107" s="19" t="s">
         <v>357</v>
       </c>
-      <c r="D107" s="20"/>
+      <c r="D107" s="18"/>
       <c r="E107" s="7"/>
       <c r="F107" s="7"/>
       <c r="G107" s="7"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108" s="20" t="s">
+      <c r="A108" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="B108" s="20" t="s">
+      <c r="B108" s="18" t="s">
         <v>380</v>
       </c>
-      <c r="C108" s="12" t="s">
+      <c r="C108" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D108" s="20"/>
+      <c r="D108" s="18"/>
       <c r="E108" s="7"/>
       <c r="F108" s="7"/>
       <c r="G108" s="7"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" s="18" t="s">
+      <c r="A109" s="20" t="s">
         <v>374</v>
       </c>
-      <c r="B109" s="18" t="s">
+      <c r="B109" s="20" t="s">
         <v>375</v>
       </c>
-      <c r="C109" s="18" t="s">
+      <c r="C109" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="D109" s="18"/>
-      <c r="E109" s="19"/>
-      <c r="F109" s="19"/>
-      <c r="G109" s="19"/>
+      <c r="D109" s="20"/>
+      <c r="E109" s="16"/>
+      <c r="F109" s="16"/>
+      <c r="G109" s="16"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" s="22" t="s">
+      <c r="A110" s="19" t="s">
         <v>384</v>
       </c>
-      <c r="B110" s="22" t="s">
+      <c r="B110" s="19" t="s">
         <v>385</v>
       </c>
-      <c r="C110" s="22" t="s">
+      <c r="C110" s="19" t="s">
         <v>358</v>
       </c>
-      <c r="D110" s="12"/>
+      <c r="D110" s="19"/>
       <c r="E110" s="7"/>
       <c r="F110" s="7"/>
       <c r="G110" s="7"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" s="21" t="s">
+      <c r="A111" s="19" t="s">
         <v>344</v>
       </c>
-      <c r="B111" s="21" t="s">
+      <c r="B111" s="19" t="s">
         <v>354</v>
       </c>
-      <c r="C111" s="21" t="s">
+      <c r="C111" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="D111" s="12"/>
+      <c r="D111" s="19"/>
       <c r="E111" s="7"/>
       <c r="F111" s="7"/>
       <c r="G111" s="7"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="21" t="s">
+      <c r="A112" s="19" t="s">
         <v>345</v>
       </c>
-      <c r="B112" s="21" t="s">
+      <c r="B112" s="19" t="s">
         <v>355</v>
       </c>
-      <c r="C112" s="21" t="s">
+      <c r="C112" s="19" t="s">
         <v>357</v>
       </c>
-      <c r="D112" s="12"/>
+      <c r="D112" s="19"/>
       <c r="E112" s="7"/>
       <c r="F112" s="7"/>
       <c r="G112" s="7"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A113" s="21" t="s">
+      <c r="A113" s="19" t="s">
         <v>339</v>
       </c>
-      <c r="B113" s="21" t="s">
+      <c r="B113" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="C113" s="21" t="s">
+      <c r="C113" s="19" t="s">
         <v>359</v>
       </c>
-      <c r="D113" s="12"/>
+      <c r="D113" s="19"/>
       <c r="E113" s="7"/>
       <c r="F113" s="7"/>
       <c r="G113" s="7"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" s="21" t="s">
+      <c r="A114" s="19" t="s">
         <v>340</v>
       </c>
-      <c r="B114" s="21" t="s">
+      <c r="B114" s="19" t="s">
         <v>350</v>
       </c>
-      <c r="C114" s="21" t="s">
+      <c r="C114" s="19" t="s">
         <v>280</v>
       </c>
-      <c r="D114" s="12"/>
+      <c r="D114" s="19"/>
       <c r="E114" s="7"/>
       <c r="F114" s="7"/>
       <c r="G114" s="7"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A115" s="21" t="s">
+      <c r="A115" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="B115" s="21" t="s">
+      <c r="B115" s="19" t="s">
         <v>351</v>
       </c>
-      <c r="C115" s="21" t="s">
+      <c r="C115" s="19" t="s">
         <v>357</v>
       </c>
-      <c r="D115" s="12"/>
+      <c r="D115" s="19"/>
       <c r="E115" s="7"/>
       <c r="F115" s="7"/>
       <c r="G115" s="7"/>
@@ -4359,13 +4350,13 @@
       <c r="G158" s="8"/>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A159" s="15" t="s">
+      <c r="A159" s="21" t="s">
         <v>331</v>
       </c>
-      <c r="B159" s="15" t="s">
+      <c r="B159" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="C159" s="15" t="s">
+      <c r="C159" s="21" t="s">
         <v>333</v>
       </c>
       <c r="D159" s="8"/>
@@ -4980,13 +4971,13 @@
       <c r="G199" s="3"/>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A200" s="15" t="s">
+      <c r="A200" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="B200" s="15" t="s">
+      <c r="B200" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="C200" s="15" t="s">
+      <c r="C200" s="21" t="s">
         <v>333</v>
       </c>
       <c r="D200" s="3"/>
@@ -5205,13 +5196,13 @@
       <c r="G214" s="3"/>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A215" s="14" t="s">
+      <c r="A215" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="B215" s="14" t="s">
+      <c r="B215" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="C215" s="14" t="s">
+      <c r="C215" s="3" t="s">
         <v>248</v>
       </c>
       <c r="D215" s="3"/>
